--- a/artfynd/A 36160-2024 artfynd.xlsx
+++ b/artfynd/A 36160-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123419361</v>
       </c>
       <c r="B2" t="n">
-        <v>98285</v>
+        <v>98287</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -808,7 +808,7 @@
         <v>123419363</v>
       </c>
       <c r="B3" t="n">
-        <v>98285</v>
+        <v>98287</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 36160-2024 artfynd.xlsx
+++ b/artfynd/A 36160-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123419361</v>
+        <v>123419363</v>
       </c>
       <c r="B2" t="n">
-        <v>98287</v>
+        <v>98293</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -724,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>604727</v>
+        <v>604830</v>
       </c>
       <c r="R2" t="n">
-        <v>6778728</v>
+        <v>6778659</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,7 +754,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>2024_2272</t>
+          <t>2024_2270</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -774,7 +774,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -805,10 +805,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123419363</v>
+        <v>123419361</v>
       </c>
       <c r="B3" t="n">
-        <v>98287</v>
+        <v>98293</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -840,7 +840,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -854,10 +854,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>604830</v>
+        <v>604727</v>
       </c>
       <c r="R3" t="n">
-        <v>6778659</v>
+        <v>6778728</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -884,7 +884,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>2024_2270</t>
+          <t>2024_2272</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -894,7 +894,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 36160-2024 artfynd.xlsx
+++ b/artfynd/A 36160-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123419361</v>
+        <v>123419363</v>
       </c>
       <c r="B2" t="n">
-        <v>98296</v>
+        <v>98313</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -724,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>604727</v>
+        <v>604830</v>
       </c>
       <c r="R2" t="n">
-        <v>6778728</v>
+        <v>6778659</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,7 +754,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>2024_2272</t>
+          <t>2024_2270</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -774,7 +774,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -805,10 +805,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123419363</v>
+        <v>123419361</v>
       </c>
       <c r="B3" t="n">
-        <v>98296</v>
+        <v>98313</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -840,7 +840,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -854,10 +854,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>604830</v>
+        <v>604727</v>
       </c>
       <c r="R3" t="n">
-        <v>6778659</v>
+        <v>6778728</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -884,7 +884,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>2024_2270</t>
+          <t>2024_2272</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -894,7 +894,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 36160-2024 artfynd.xlsx
+++ b/artfynd/A 36160-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123419363</v>
+        <v>123419361</v>
       </c>
       <c r="B2" t="n">
-        <v>98313</v>
+        <v>98419</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -724,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>604830</v>
+        <v>604727</v>
       </c>
       <c r="R2" t="n">
-        <v>6778659</v>
+        <v>6778728</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,7 +754,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>2024_2270</t>
+          <t>2024_2272</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -774,7 +774,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -805,10 +805,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123419361</v>
+        <v>123419363</v>
       </c>
       <c r="B3" t="n">
-        <v>98313</v>
+        <v>98419</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -840,7 +840,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -854,10 +854,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>604727</v>
+        <v>604830</v>
       </c>
       <c r="R3" t="n">
-        <v>6778728</v>
+        <v>6778659</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -884,7 +884,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>2024_2272</t>
+          <t>2024_2270</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -894,7 +894,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 36160-2024 artfynd.xlsx
+++ b/artfynd/A 36160-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123419361</v>
       </c>
       <c r="B2" t="n">
-        <v>98419</v>
+        <v>98421</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -808,7 +808,7 @@
         <v>123419363</v>
       </c>
       <c r="B3" t="n">
-        <v>98419</v>
+        <v>98421</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 36160-2024 artfynd.xlsx
+++ b/artfynd/A 36160-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123419361</v>
       </c>
       <c r="B2" t="n">
-        <v>98421</v>
+        <v>97996</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -808,7 +808,7 @@
         <v>123419363</v>
       </c>
       <c r="B3" t="n">
-        <v>98421</v>
+        <v>97996</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 36160-2024 artfynd.xlsx
+++ b/artfynd/A 36160-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123419361</v>
+        <v>123419363</v>
       </c>
       <c r="B2" t="n">
         <v>97996</v>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -724,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>604727</v>
+        <v>604830</v>
       </c>
       <c r="R2" t="n">
-        <v>6778728</v>
+        <v>6778659</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,7 +754,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>2024_2272</t>
+          <t>2024_2270</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -774,7 +774,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -805,7 +805,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123419363</v>
+        <v>123419361</v>
       </c>
       <c r="B3" t="n">
         <v>97996</v>
@@ -840,7 +840,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -854,10 +854,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>604830</v>
+        <v>604727</v>
       </c>
       <c r="R3" t="n">
-        <v>6778659</v>
+        <v>6778728</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -884,7 +884,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>2024_2270</t>
+          <t>2024_2272</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -894,7 +894,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AD3" t="b">
